--- a/exemplaires-import-biens/exemplaires-import-biens/exemplaire_biens.xlsx
+++ b/exemplaires-import-biens/exemplaires-import-biens/exemplaire_biens.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76EC01A6-9C6B-4605-9ED6-FB15C46AAC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36108EAD-8705-4F73-8595-D4494C79ABB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -112,24 +112,6 @@
     <t>Nombre facade</t>
   </si>
   <si>
-    <t>B1</t>
-  </si>
-  <si>
-    <t>B2</t>
-  </si>
-  <si>
-    <t>B3</t>
-  </si>
-  <si>
-    <t>B4</t>
-  </si>
-  <si>
-    <t>B5</t>
-  </si>
-  <si>
-    <t>B6</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
@@ -139,7 +121,25 @@
     <t>3</t>
   </si>
   <si>
-    <t>B7</t>
+    <t>AB1</t>
+  </si>
+  <si>
+    <t>AB2</t>
+  </si>
+  <si>
+    <t>AB3</t>
+  </si>
+  <si>
+    <t>AB4</t>
+  </si>
+  <si>
+    <t>AB5</t>
+  </si>
+  <si>
+    <t>AB6</t>
+  </si>
+  <si>
+    <t>AB7</t>
   </si>
 </sst>
 </file>
@@ -683,10 +683,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="D2" s="2">
         <v>0</v>
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>31</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="D3" s="12">
         <v>30</v>
@@ -770,10 +770,10 @@
         <v>0</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>38</v>
       </c>
       <c r="D4" s="12">
         <v>820</v>
@@ -815,10 +815,10 @@
         <v>0</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D5" s="12">
         <v>820</v>
@@ -860,10 +860,10 @@
         <v>0</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D6" s="12">
         <v>820</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D7" s="12">
         <v>820</v>
@@ -953,7 +953,7 @@
         <v>39</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D8" s="12">
         <v>820</v>
